--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakshitha.M\IdeaProjects\new\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF0D589-C22A-4563-8C01-576F6D43AB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500"/>
+    <workbookView xWindow="9420" yWindow="5050" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
   <si>
     <t>lang_code</t>
   </si>
@@ -48,12 +49,15 @@
   </si>
   <si>
     <t>service-account-mosip-resident-client</t>
+  </si>
+  <si>
+    <t>UTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -429,17 +433,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="32.26953125" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -467,7 +471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -478,6 +482,34 @@
         <v>7</v>
       </c>
       <c r="D3" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="b">
         <v>1</v>
       </c>
     </row>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF0D589-C22A-4563-8C01-576F6D43AB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234425AE-95E6-4013-862D-20634B315B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9420" yWindow="5050" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3400" yWindow="7820" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>lang_code</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>eng</t>
-  </si>
-  <si>
-    <t>MOR</t>
   </si>
   <si>
     <t>globaladmin</t>
@@ -434,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.26953125" customWidth="1"/>
@@ -462,10 +459,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>1</v>
@@ -476,40 +473,12 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="b">
         <v>1</v>
       </c>
     </row>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakshitha.M\IdeaProjects\new\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234425AE-95E6-4013-862D-20634B315B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3400" yWindow="7820" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -42,19 +41,19 @@
     <t>eng</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>globaladmin</t>
   </si>
   <si>
     <t>service-account-mosip-resident-client</t>
-  </si>
-  <si>
-    <t>UTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -430,17 +429,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="32.26953125" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -454,29 +453,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakshitha.M\IdeaProjects\new\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E808A756-8333-4212-8A14-0F253A177FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500"/>
+    <workbookView xWindow="5790" yWindow="6240" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,19 +42,19 @@
     <t>eng</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
     <t>globaladmin</t>
   </si>
   <si>
     <t>service-account-mosip-resident-client</t>
+  </si>
+  <si>
+    <t>UTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -429,17 +430,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="32.26953125" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,29 +454,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E808A756-8333-4212-8A14-0F253A177FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522F9BEE-3140-4BA3-ADE7-ED16BBF0B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="6240" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5655" yWindow="3180" windowWidth="21600" windowHeight="11055" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <t>service-account-mosip-resident-client</t>
   </si>
   <si>
-    <t>UTO</t>
+    <t>MOR</t>
   </si>
 </sst>
 </file>
@@ -432,15 +432,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="32.26953125" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -454,7 +454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -468,7 +468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakshitha.M\IdeaProjects\new\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522F9BEE-3140-4BA3-ADE7-ED16BBF0B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="3180" windowWidth="21600" windowHeight="11055" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,19 +41,19 @@
     <t>eng</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>globaladmin</t>
   </si>
   <si>
     <t>service-account-mosip-resident-client</t>
-  </si>
-  <si>
-    <t>MOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -430,7 +429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -459,10 +458,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>1</v>
@@ -473,10 +472,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakshitha.M\IdeaProjects\new\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C084347-6495-4DA3-BBAA-F5155DE63537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500"/>
+    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -41,19 +42,19 @@
     <t>eng</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
     <t>globaladmin</t>
   </si>
   <si>
     <t>service-account-mosip-resident-client</t>
+  </si>
+  <si>
+    <t>UTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -429,17 +430,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.265625" customWidth="1"/>
+    <col min="2" max="2" width="10.86328125" customWidth="1"/>
+    <col min="3" max="3" width="32.265625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,29 +454,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakshitha.M\IdeaProjects\new\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C084347-6495-4DA3-BBAA-F5155DE63537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -42,19 +41,19 @@
     <t>eng</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>globaladmin</t>
   </si>
   <si>
     <t>service-account-mosip-resident-client</t>
-  </si>
-  <si>
-    <t>UTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -430,17 +429,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.265625" customWidth="1"/>
-    <col min="2" max="2" width="10.86328125" customWidth="1"/>
-    <col min="3" max="3" width="32.265625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -454,29 +453,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>

--- a/mosip_master/xlsx/zone_user.xlsx
+++ b/mosip_master/xlsx/zone_user.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakshitha.M\IdeaProjects\new\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF4C7D4-78F3-4F15-9D67-F1B54C6EF112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500"/>
+    <workbookView xWindow="4230" yWindow="4230" windowWidth="21600" windowHeight="11055" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -41,19 +42,19 @@
     <t>eng</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
     <t>globaladmin</t>
   </si>
   <si>
     <t>service-account-mosip-resident-client</t>
+  </si>
+  <si>
+    <t>UTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -69,7 +70,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -429,17 +430,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.265625" customWidth="1"/>
+    <col min="2" max="2" width="10.86328125" customWidth="1"/>
+    <col min="3" max="3" width="32.265625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,29 +454,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>
